--- a/Забрањени парови.xlsx
+++ b/Забрањени парови.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29614"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dejan\code\dejosub\sahovski-turniri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B3418B-9A4D-49B2-BBB3-D337404F7CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8094705-74BC-4A75-A4FB-D7C7FF53051F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36510" yWindow="4440" windowWidth="35070" windowHeight="22425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38730" yWindow="855" windowWidth="35070" windowHeight="22425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Владо Жарић</t>
   </si>
@@ -88,6 +88,12 @@
   </si>
   <si>
     <t>Кита Колева</t>
+  </si>
+  <si>
+    <t>Алекса Миловановић</t>
+  </si>
+  <si>
+    <t>Лана Парежанин</t>
   </si>
 </sst>
 </file>
@@ -405,10 +411,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -494,6 +500,14 @@
         <v>19</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
